--- a/DiffCheck.Core.Tests/TestData/right.xlsx
+++ b/DiffCheck.Core.Tests/TestData/right.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -34,7 +34,7 @@
     <t xml:space="preserve">D</t>
   </si>
   <si>
-    <t xml:space="preserve">E</t>
+    <t xml:space="preserve">EF</t>
   </si>
   <si>
     <t xml:space="preserve">asd</t>
@@ -115,12 +115,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -144,37 +148,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -248,7 +252,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -744,7 +748,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="n">
